--- a/data/trans_bre/IP16_n_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Clase-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 37,94</t>
+          <t>-14,44; 34,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 9,0</t>
+          <t>-20,02; 10,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 26,6</t>
+          <t>-9,64; 23,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 39,78</t>
+          <t>-2,59; 39,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 243,36</t>
+          <t>-39,24; 208,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 274,35</t>
+          <t>-8,6; 252,87</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 19,13</t>
+          <t>-31,7; 19,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 26,66</t>
+          <t>-5,97; 25,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 6,7</t>
+          <t>-25,06; 8,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,46; 4,25</t>
+          <t>-41,19; 4,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 76,12</t>
+          <t>-61,29; 79,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,23; 18,57</t>
+          <t>-74,87; 17,38</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 10,64</t>
+          <t>-44,79; 8,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 37,68</t>
+          <t>-19,78; 38,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,52; 63,23</t>
+          <t>13,6; 63,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-38,65; 21,7</t>
+          <t>-38,86; 18,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,29; 26,13</t>
+          <t>-73,8; 19,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-66,09; 603,05</t>
+          <t>-62,34; 548,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,34; 113,22</t>
+          <t>-82,3; 105,85</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 18,29</t>
+          <t>-17,27; 18,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 18,87</t>
+          <t>-2,75; 19,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 12,34</t>
+          <t>-9,4; 10,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 1,76</t>
+          <t>-39,06; -1,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 61,47</t>
+          <t>-37,46; 57,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 325,89</t>
+          <t>-20,85; 341,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 377,78</t>
+          <t>-67,49; 258,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,55; 4,13</t>
+          <t>-81,44; -4,33</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 38,53</t>
+          <t>-11,02; 36,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 15,9</t>
+          <t>-19,03; 15,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 3,06</t>
+          <t>-30,87; 1,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 31,16</t>
+          <t>-8,28; 30,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 206,88</t>
+          <t>-32,33; 210,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-71,52; 128,04</t>
+          <t>-68,35; 149,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-89,54; 40,98</t>
+          <t>-91,91; 26,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 162,11</t>
+          <t>-22,23; 168,23</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,07; 39,77</t>
+          <t>-39,72; 33,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 36,59</t>
+          <t>-29,7; 32,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,76; 11,95</t>
+          <t>-37,45; 14,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 30,12</t>
+          <t>-31,72; 30,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 114,05</t>
+          <t>-58,2; 91,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 613,34</t>
+          <t>-100,0; 376,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,58; 129,47</t>
+          <t>-58,77; 142,46</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 9,97</t>
+          <t>-11,05; 9,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 10,28</t>
+          <t>-3,96; 10,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 5,84</t>
+          <t>-7,86; 6,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 4,61</t>
+          <t>-18,35; 4,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 27,77</t>
+          <t>-24,29; 26,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 91,83</t>
+          <t>-24,45; 91,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 65,1</t>
+          <t>-49,89; 69,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 15,01</t>
+          <t>-50,46; 15,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16_n_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,46</t>
+          <t>21,01</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 34,78</t>
+          <t>-13,88; 34,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 10,14</t>
+          <t>-21,0; 10,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 23,63</t>
+          <t>-9,36; 25,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 39,97</t>
+          <t>-1,35; 40,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 208,86</t>
+          <t>-40,63; 210,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 252,87</t>
+          <t>-5,06; 287,15</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-18,5</t>
+          <t>-19,49</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-43,32%</t>
+          <t>-44,49%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 19,51</t>
+          <t>-29,54; 19,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 25,69</t>
+          <t>-5,93; 25,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 8,31</t>
+          <t>-25,49; 8,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,19; 4,09</t>
+          <t>-42,04; 4,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,29; 79,18</t>
+          <t>-61,59; 83,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,87; 17,38</t>
+          <t>-74,17; 30,44</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-12,65</t>
+          <t>-15,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-34,7%</t>
+          <t>-39,53%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-44,79; 8,68</t>
+          <t>-47,78; 7,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 38,58</t>
+          <t>-20,79; 38,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,6; 63,62</t>
+          <t>12,73; 64,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 18,5</t>
+          <t>-41,85; 15,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,8; 19,98</t>
+          <t>-74,64; 18,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,34; 548,83</t>
+          <t>-63,59; 685,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-82,3; 105,85</t>
+          <t>-83,53; 70,32</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-17,38</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-47,8%</t>
+          <t>-7,4%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 18,11</t>
+          <t>-17,24; 19,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 19,42</t>
+          <t>-3,93; 18,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 10,87</t>
+          <t>-9,29; 12,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,06; -1,2</t>
+          <t>-21,21; 13,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,46; 57,78</t>
+          <t>-34,72; 63,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 341,9</t>
+          <t>-31,52; 289,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,49; 258,14</t>
+          <t>-61,81; 395,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,44; -4,33</t>
+          <t>-47,38; 48,38</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,91</t>
+          <t>10,71</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 36,85</t>
+          <t>-11,23; 36,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 15,56</t>
+          <t>-18,81; 19,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 1,54</t>
+          <t>-31,79; 0,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 30,89</t>
+          <t>-9,6; 29,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 210,45</t>
+          <t>-35,42; 210,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-68,35; 149,73</t>
+          <t>-72,09; 189,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-91,91; 26,78</t>
+          <t>-92,94; 12,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 168,23</t>
+          <t>-24,93; 165,63</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-2,77%</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 33,42</t>
+          <t>-35,05; 37,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 32,81</t>
+          <t>-28,91; 32,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,45; 14,27</t>
+          <t>-42,53; 11,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 30,63</t>
+          <t>-34,43; 28,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 91,64</t>
+          <t>-54,54; 102,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 376,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,77; 142,46</t>
+          <t>-62,97; 120,67</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,25</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-15,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 9,18</t>
+          <t>-9,21; 11,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 10,47</t>
+          <t>-4,15; 10,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 6,23</t>
+          <t>-7,27; 5,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 4,84</t>
+          <t>-9,52; 9,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 26,82</t>
+          <t>-20,87; 34,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 91,79</t>
+          <t>-23,58; 98,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-49,89; 69,35</t>
+          <t>-44,1; 67,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 15,32</t>
+          <t>-24,57; 32,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16_n_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,183 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10,86</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,14</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,19</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21,01</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,22%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-37,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>85,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>80,58%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.5417253821830857</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.120484703192188</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.272524417493378</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5.105845272945746</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.08664725633763821</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4072532937617621</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.9892984096730419</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.8279988289501956</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-13,88; 34,39</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-21,0; 10,12</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-9,36; 25,23</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-1,35; 40,61</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-40,63; 210,28</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-5,06; 287,15</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.068858634516599</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.753581188539675</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.407008122171161</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.150110023523698</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.6383330521888285</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.195439759016949</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.428323856335816</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.415694652069333</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.780389290434576</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.44465558442405</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.305146487443414</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>3.227199817338985</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-7,14</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-9,34</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-19,49</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-16,96%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>201,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-64,62%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-44,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-29,54; 19,34</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,93; 25,87</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-25,49; 8,74</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-42,04; 4,77</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-61,59; 83,95</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-74,17; 30,44</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.9720316900944062</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.40363394221693</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.862604315244145</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-5.056940015360442</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1111098631122931</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>4.918894693943022</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.7625306683994713</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.4663437856895631</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-20,75</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8,26</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>34,44</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-15,5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-38,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>38,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-39,53%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.818267349818509</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5014087558907158</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.348304594079399</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-12.49725222806135</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6333119669367033</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="n">
+        <v>-0.790702980732559</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-47,78; 7,46</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-20,79; 38,61</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12,73; 64,84</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-41,85; 15,45</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-74,64; 18,87</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-63,59; 685,74</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-83,53; 70,32</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.101664423921687</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.633234228520896</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5371013254479973</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.249376928590558</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.242697650538144</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="n">
+        <v>0.3055596510534476</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +803,193 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,63</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>65,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-7,4%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-6.484188631425812</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.874016219289955</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.926906916569052</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-6.127476605244107</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5376345038504264</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.2829284675826305</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.5921536793869041</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-17,24; 19,61</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,93; 18,85</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-9,29; 12,38</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-21,21; 13,61</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-34,72; 63,5</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-31,52; 289,15</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-61,81; 395,67</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-47,38; 48,38</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-13.43249866714463</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.146086049632383</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.804330240821051</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-14.78521422037804</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.8279573108586628</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
+        <v>-0.9110859614582264</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.152905022215131</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.847746690396312</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.36411575936605</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.03201760011228694</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1507193892175044</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
+        <v>0.2498612094658985</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>13,83</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,21</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-13,13</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,71</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>49,43%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-6,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-58,74%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>37,47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-11,23; 36,89</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-18,81; 19,06</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-31,79; 0,43</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-9,6; 29,94</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-35,42; 210,17</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-72,09; 189,73</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-92,94; 12,31</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-24,93; 165,63</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.1894572311873094</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.453980911495673</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8102109227556135</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.9240098504401508</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.0246114112540821</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.510161252327928</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.5335977334334063</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.10567234171783</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-2,65</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-10,41</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-11,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-49,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-2,77%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.01521940316903</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.479431697683915</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.9712838950699496</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.577306232383584</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4922734222130987</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4420636990550316</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5210541874958189</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.509882324342913</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-35,05; 37,34</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-28,91; 32,4</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-42,53; 11,35</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-34,43; 28,18</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-54,54; 102,52</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-62,97; 120,67</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.841752919755022</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.633794638553487</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.089260183541037</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.647272003746319</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.698733973377621</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.86668578056481</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>5.994657163443233</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.5630806642326144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +997,289 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,11</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,3%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-5,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>2.316815941943576</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.3667641400140448</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.206693276557449</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>3.336707492530432</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.441127144740348</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.0926957751290422</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.5503091139695568</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.5379228020516155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-9,21; 11,85</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,15; 10,27</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-7,27; 5,68</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-9,52; 9,41</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-20,87; 34,75</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-23,58; 98,69</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-44,1; 67,41</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-24,57; 32,17</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.480051729867367</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.156970251563685</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.755830827739463</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.679468944402672</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3853997398047284</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.7353537606769722</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.904684524450149</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2603347609382773</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.858241286390523</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.629588523531208</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.5276910438730298</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>9.094633501454833</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2.853948226142768</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2.24364826286743</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.6258034326327421</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>2.156428848417623</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-2.90583315008566</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1.71626471184038</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-0.7555016898771947</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.418145439848903</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3405802453970428</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.3820346594795984</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.2470558152942976</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.1676244276982106</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-10.57078341977579</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-7.105484429039175</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-5.057536771037117</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-9.173837226290285</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.8015762110274329</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="n">
+        <v>-0.7341793936678153</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3.549543373163967</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3.688754667931516</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>4.18650121401951</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>5.951760208185167</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.9772176137414539</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="n">
+        <v>1.656185886029618</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-1.053412001796016</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.6381323589225742</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.09151345377725467</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.1191407905535485</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.1335079302811085</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.2154921759284356</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.04315337301476409</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.01466560322221394</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-3.608284320054027</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.9248798576824767</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.037347458929987</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-2.70245057202503</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.3841694889509628</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.2643879897404257</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.4004040665431448</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.2793009046871069</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.357364787342677</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.21323214186943</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.316878719117543</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.28300134909033</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.2044096638269086</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.001959859480258</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.8500532081496631</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.3309069930953858</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1287,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
